--- a/Deterministic/Model objective analysis/quantity discount/data/Starting_point.xlsx
+++ b/Deterministic/Model objective analysis/quantity discount/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model objective analysis/quantity discount/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD7E713-1AF3-4E4D-91B0-05E744E35DB1}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB48D592-FC4E-4829-BE1E-BACEEDA9489E}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -558,9 +558,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -571,7 +571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,7 +582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -593,7 +593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -604,7 +604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -626,7 +626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -637,7 +637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -648,7 +648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -670,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -681,7 +681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -692,7 +692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -712,15 +712,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E851515-DB43-462D-9C92-F50748C0A12A}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="8.88671875" style="2"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.85546875" style="2"/>
-    <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="16.109375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -737,7 +737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -754,7 +754,7 @@
         <v>13299</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -771,7 +771,7 @@
         <v>12505</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -788,7 +788,7 @@
         <v>13547</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -805,7 +805,7 @@
         <v>6547</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -822,7 +822,7 @@
         <v>90279</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -839,7 +839,7 @@
         <v>180177</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -856,7 +856,7 @@
         <v>13305</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -873,7 +873,7 @@
         <v>8948</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -890,7 +890,7 @@
         <v>140932</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -907,7 +907,7 @@
         <v>17896</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -924,7 +924,7 @@
         <v>31318</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -941,7 +941,7 @@
         <v>53688</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -958,7 +958,7 @@
         <v>43365</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -975,7 +975,7 @@
         <v>40214</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -992,7 +992,7 @@
         <v>219201</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>61221</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>84681</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13464</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>5391</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>56510</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>185663</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>13</v>
       </c>
@@ -1188,13 +1188,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF8CA8F-1DBE-42B3-8633-48C2ED5062E9}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>398056107.80000001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>27968660.210000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1226,39 +1226,39 @@
         <v>410128001.42000002</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="8">
-        <v>590379508</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5903795089</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="9">
-        <v>280763726</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2807637269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="9">
-        <v>879375105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8793751059</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="9">
-        <v>83171840</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>831718409</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>7682600</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>3278988.3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>2828944.58</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>116834378.34999999</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>27</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>5298997.59</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>30290394.390000001</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>43271991.979999997</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>86543983.959999993</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>242285505</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>10</v>
       </c>
@@ -1347,13 +1347,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903BEB0C-00BA-4B81-9CB6-933B54D27020}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>45</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
